--- a/satisfaction_surveys/035_it_service_satisfaction_survey--satisfaction_surveys.xlsx
+++ b/satisfaction_surveys/035_it_service_satisfaction_survey--satisfaction_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -826,8 +826,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="43" customWidth="1" min="2" max="2"/>
-    <col width="43" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'not_satisfied'}</t>
+          <t>not_satisfied</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Not Satisfied'}</t>
+          <t>Not Satisfied</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'slightly_satisfied'}</t>
+          <t>slightly_satisfied</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Slightly Satisfied'}</t>
+          <t>Slightly Satisfied</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'slightly_dissatisfied'}</t>
+          <t>slightly_dissatisfied</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Slightly Dissatisfied'}</t>
+          <t>Slightly Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'dissatisfied'}</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Dissatisfied'}</t>
+          <t>Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'help_desk'}</t>
+          <t>help_desk</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Help Desk'}</t>
+          <t>Help Desk</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'project_management'}</t>
+          <t>project_management</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Project Management'}</t>
+          <t>Project Management</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'service_management'}</t>
+          <t>service_management</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Service Management'}</t>
+          <t>Service Management</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'frequently'}</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Frequently'}</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
@@ -1025,12 +1025,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Occasionally'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1093,12 +1093,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1110,12 +1110,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'online_portal'}</t>
+          <t>online_portal</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Online Portal'}</t>
+          <t>Online Portal</t>
         </is>
       </c>
     </row>
@@ -1127,12 +1127,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1178,12 +1178,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'online_chat'}</t>
+          <t>online_chat</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Online Chat'}</t>
+          <t>Online Chat</t>
         </is>
       </c>
     </row>
@@ -1195,12 +1195,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'visit_office'}</t>
+          <t>visit_office</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Visit Office'}</t>
+          <t>Visit Office</t>
         </is>
       </c>
     </row>
@@ -1212,12 +1212,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'faster_response_time'}</t>
+          <t>faster_response_time</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Faster Response Time'}</t>
+          <t>Faster Response Time</t>
         </is>
       </c>
     </row>
@@ -1229,12 +1229,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'easier_access_to_information'}</t>
+          <t>easier_access_to_information</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Easier Access to Information'}</t>
+          <t>Easier Access to Information</t>
         </is>
       </c>
     </row>
@@ -1246,12 +1246,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'better_communication'}</t>
+          <t>better_communication</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Better Communication'}</t>
+          <t>Better Communication</t>
         </is>
       </c>
     </row>
@@ -1263,12 +1263,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1280,12 +1280,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Very Good'}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
@@ -1297,12 +1297,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1314,12 +1314,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'average'}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Average'}</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -1331,12 +1331,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'very_poor'}</t>
+          <t>very_poor</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Very Poor'}</t>
+          <t>Very Poor</t>
         </is>
       </c>
     </row>
